--- a/doctool/test/auto/scenario10/システム機能設計書_サンプル_S10_レビュー記録票_expected.xlsx
+++ b/doctool/test/auto/scenario10/システム機能設計書_サンプル_S10_レビュー記録票_expected.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr filterPrivacy="1" updateLinks="never" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F839D05-AEC1-4EC3-A719-AD44776C22A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{216B2CB1-55CA-4DF1-95E1-3DF84E6C5F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2250" yWindow="5655" windowWidth="24285" windowHeight="13710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="レビュー実施状況" sheetId="3" r:id="rId1"/>
